--- a/data/task_breakdown.xlsx
+++ b/data/task_breakdown.xlsx
@@ -1,34 +1,73 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sites.ey.com/sites/Nordea-CustomerRemediation/Shared Documents/General/11 - Dashboard/data/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="15" documentId="11_A8176D4C7C56131E3EEBC84282AE758A4E75AAAD" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E27F26BD-41AD-4261-BFAB-7FEEB81FA3AE}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+  <si>
+    <t>Task</t>
+  </si>
+  <si>
+    <t>Not_Started</t>
+  </si>
+  <si>
+    <t>In_Progress</t>
+  </si>
+  <si>
+    <t>Completed</t>
+  </si>
+  <si>
+    <t>Customer queries</t>
+  </si>
+  <si>
+    <t>Hybrid cases</t>
+  </si>
+  <si>
+    <t>Letter rejections/returns</t>
+  </si>
+  <si>
+    <t>Payment rejections/returns</t>
+  </si>
+  <si>
+    <t>Special and Exempted cases</t>
+  </si>
+  <si>
+    <t>Testing</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -47,80 +86,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -408,129 +388,105 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Task</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Not_Started</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>In_Progress</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Customer queries</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2">
+        <v>0</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
         <v>5</v>
       </c>
-      <c r="C2" t="n">
-        <v>5</v>
-      </c>
-      <c r="D2" t="n">
-        <v>10</v>
+      <c r="B3">
+        <v>1811</v>
+      </c>
+      <c r="C3">
+        <v>163</v>
+      </c>
+      <c r="D3">
+        <v>5865</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Hybrid cases</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>3152</v>
-      </c>
-      <c r="C3" t="n">
-        <v>145</v>
-      </c>
-      <c r="D3" t="n">
-        <v>4504</v>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4">
+        <v>0</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Letter rejections/returns</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>30</v>
-      </c>
-      <c r="C4" t="n">
-        <v>35</v>
-      </c>
-      <c r="D4" t="n">
-        <v>63</v>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5">
+        <v>0</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Payment rejections/returns</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>15</v>
-      </c>
-      <c r="C5" t="n">
-        <v>15</v>
-      </c>
-      <c r="D5" t="n">
-        <v>30</v>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6">
+        <v>0</v>
+      </c>
+      <c r="C6">
+        <v>54</v>
+      </c>
+      <c r="D6">
+        <v>34</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Special and Exempted cases</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>10</v>
-      </c>
-      <c r="C6" t="n">
-        <v>10</v>
-      </c>
-      <c r="D6" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Testing</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>0</v>
-      </c>
-      <c r="C7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" t="n">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7">
+        <v>0</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7">
         <v>0</v>
       </c>
     </row>
@@ -540,6 +496,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100D9F28F5819300A43901E9DBC513AE4A8" ma:contentTypeVersion="6" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0baf57f2338ee7e444e82289da7848b2">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="40111ba8-f904-4ecf-a49d-62383d8f24ce" xmlns:ns3="1f46f138-9cbd-41b8-9ede-c2ff327f64b5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="02446be83e1a77402352026bad75407b" ns2:_="" ns3:_="">
     <xsd:import namespace="40111ba8-f904-4ecf-a49d-62383d8f24ce"/>
@@ -716,29 +687,38 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1EC0A359-2A59-4DE4-B71A-F490E89AB2F0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5CCFD296-E39C-4EA1-9541-2962B4BD63AE}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0164D447-1811-42BA-B5A8-D8508D519024}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0164D447-1811-42BA-B5A8-D8508D519024}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5CCFD296-E39C-4EA1-9541-2962B4BD63AE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1EC0A359-2A59-4DE4-B71A-F490E89AB2F0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="40111ba8-f904-4ecf-a49d-62383d8f24ce"/>
+    <ds:schemaRef ds:uri="1f46f138-9cbd-41b8-9ede-c2ff327f64b5"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/data/task_breakdown.xlsx
+++ b/data/task_breakdown.xlsx
@@ -511,8 +511,8 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100D9F28F5819300A43901E9DBC513AE4A8" ma:contentTypeVersion="6" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0baf57f2338ee7e444e82289da7848b2">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="40111ba8-f904-4ecf-a49d-62383d8f24ce" xmlns:ns3="1f46f138-9cbd-41b8-9ede-c2ff327f64b5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="02446be83e1a77402352026bad75407b" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x010100D9F28F5819300A43901E9DBC513AE4A8" ma:contentTypeVersion="6" ma:contentTypeDescription="Opret et nyt dokument." ma:contentTypeScope="" ma:versionID="25cf4ea28c43452cb8a3259f612469bf">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="40111ba8-f904-4ecf-a49d-62383d8f24ce" xmlns:ns3="1f46f138-9cbd-41b8-9ede-c2ff327f64b5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a4c398a66158f28d13f94d1796e970fb" ns2:_="" ns3:_="">
     <xsd:import namespace="40111ba8-f904-4ecf-a49d-62383d8f24ce"/>
     <xsd:import namespace="1f46f138-9cbd-41b8-9ede-c2ff327f64b5"/>
     <xsd:element name="properties">
@@ -561,7 +561,7 @@
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="1f46f138-9cbd-41b8-9ede-c2ff327f64b5" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="10" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+    <xsd:element name="SharedWithUsers" ma:index="10" nillable="true" ma:displayName="Delt med" ma:internalName="SharedWithUsers" ma:readOnly="true">
       <xsd:complexType>
         <xsd:complexContent>
           <xsd:extension base="dms:UserMulti">
@@ -580,7 +580,7 @@
         </xsd:complexContent>
       </xsd:complexType>
     </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="11" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+    <xsd:element name="SharedWithDetails" ma:index="11" nillable="true" ma:displayName="Delt med detaljer" ma:internalName="SharedWithDetails" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note">
           <xsd:maxLength value="255"/>
@@ -597,8 +597,8 @@
         <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Indholdstype"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Titel"/>
         <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
         <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
@@ -705,20 +705,5 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1EC0A359-2A59-4DE4-B71A-F490E89AB2F0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="40111ba8-f904-4ecf-a49d-62383d8f24ce"/>
-    <ds:schemaRef ds:uri="1f46f138-9cbd-41b8-9ede-c2ff327f64b5"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{53C94D47-C5BB-4265-BCC4-E8B1DF9388A9}"/>
 </file>